--- a/outputs/Mixed_Metabolic_Cohort_Student_Express_Report.xlsx
+++ b/outputs/Mixed_Metabolic_Cohort_Student_Express_Report.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>DerSimonian-Laird random-effects evidence pooling established a statistically significant treatment effect for bmi: pooled effect size = MD -0.70 (95% CI: [-1.17, -0.23]) (95% CI: [-1.17, -0.23], p = 0.0034). Between-study heterogeneity was quantified at I² = 0.0%, confirming a robust and generalizable direction of clinical benefit across study populations.</t>
+          <t>DerSimonian-Laird random-effects evidence pooling established a statistically significant treatment effect for bmi: pooled effect size = MD -0.70 (95% CI: [-1.17, -0.23]) (95% CI: [-1.17, -0.23], p = 0.0034). Between-study heterogeneity was quantified at I² = N/A (k=1), confirming a robust and generalizable direction of clinical benefit across study populations.</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>0.0% (Low Heterogeneity (High Consistency across trials))</t>
+          <t>N/A (k=1) (Not Applicable (Single Independent Study; between-study variance cannot be estimated))</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>Report I² = 0.0% (between-study variance τ² = 0.0000).</t>
+          <t>Report I² = N/A (k=1) (between-study variance τ² = N/A (k=1)).</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
